--- a/data/trans_orig/P3A$yo-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>186588</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167074</t>
+          <t>165114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206429</t>
+          <t>201308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>264925</t>
+          <t>290022</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249691</t>
+          <t>277295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273876</t>
+          <t>298652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>473523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>427060</t>
+          <t>449896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474473</t>
+          <t>493567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>165973</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141215</t>
+          <t>160137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186432</t>
+          <t>197800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78290</t>
+          <t>79042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66039</t>
+          <t>67346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>91181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>244263</t>
+          <t>258565</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220689</t>
+          <t>234943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270095</t>
+          <t>282990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103270</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81788</t>
+          <t>80495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>116325</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83200</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70397</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100119</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>186470</t>
+          <t>193412</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159578</t>
+          <t>169791</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215935</t>
+          <t>217033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39557</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>43178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>375996</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>346819</t>
+          <t>361875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401491</t>
+          <t>414307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>471212</t>
+          <t>497943</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455200</t>
+          <t>479610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>483614</t>
+          <t>511814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>847208</t>
+          <t>886854</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>812061</t>
+          <t>852899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877282</t>
+          <t>915286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>261595</t>
+          <t>278156</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>232091</t>
+          <t>249120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288315</t>
+          <t>305957</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158596</t>
+          <t>171614</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140362</t>
+          <t>151425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177746</t>
+          <t>192840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>420191</t>
+          <t>449770</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386690</t>
+          <t>411415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>453908</t>
+          <t>484185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>175138</t>
+          <t>169824</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147234</t>
+          <t>139760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211224</t>
+          <t>201114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>136140</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118983</t>
+          <t>123715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156562</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>311278</t>
+          <t>314723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274645</t>
+          <t>278286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349972</t>
+          <t>350597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>35224</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48231</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>64433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>29288</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>40451</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>240290</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227949</t>
+          <t>225113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255290</t>
+          <t>252900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>311471</t>
+          <t>318735</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>300583</t>
+          <t>308112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320661</t>
+          <t>327186</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,27 +2385,27 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>553619</t>
+          <t>559025</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>534332</t>
+          <t>540830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>569993</t>
+          <t>576194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>137457</t>
+          <t>136811</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120941</t>
+          <t>120503</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>154760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>108366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89616</t>
+          <t>94040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118639</t>
+          <t>121861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>241084</t>
+          <t>245177</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>219482</t>
+          <t>221426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>262307</t>
+          <t>265050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>81088</t>
+          <t>79227</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99246</t>
+          <t>97596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>79295</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>65722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95629</t>
+          <t>96047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>160383</t>
+          <t>159156</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138835</t>
+          <t>138743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>183856</t>
+          <t>182681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,67 +2689,67 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>28401</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>21457</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>37827</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>3,2%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>28625</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>21264</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>36609</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>20916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>27566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,22 +2837,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>553</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>649</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202930</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179981</t>
+          <t>214471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>223721</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>430401</t>
+          <t>372803</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>409158</t>
+          <t>353270</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>449595</t>
+          <t>386126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>633330</t>
+          <t>613715</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>598681</t>
+          <t>581237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>675463</t>
+          <t>643085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>159071</t>
+          <t>189003</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136399</t>
+          <t>163947</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180360</t>
+          <t>217035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>73945</t>
+          <t>82960</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96803</t>
+          <t>97766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>233015</t>
+          <t>271963</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>163713</t>
+          <t>241845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>273440</t>
+          <t>302030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>63417</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>83261</t>
+          <t>89345</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86773</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>115756</t>
+          <t>132499</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>154572</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>180895</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>149298</t>
+          <t>171601</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>163448</t>
+          <t>187858</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>247405</t>
+          <t>216270</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>207422</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>253181</t>
+          <t>221388</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>404498</t>
+          <t>397164</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>392750</t>
+          <t>384815</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>416839</t>
+          <t>407013</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>63585</t>
+          <t>73327</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65513</t>
+          <t>62552</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>103037</t>
+          <t>115745</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>122380</t>
+          <t>130361</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>87405</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>75346</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88581</t>
+          <t>99355</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>147866</t>
+          <t>107953</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117977</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>198378</t>
+          <t>118902</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>224982</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>190882</t>
+          <t>177772</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>294198</t>
+          <t>211159</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>207574</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>193669</t>
+          <t>196326</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>219858</t>
+          <t>220581</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>235819</t>
+          <t>242112</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>228734</t>
+          <t>235011</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>241805</t>
+          <t>247694</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>443393</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>428595</t>
+          <t>435028</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>457375</t>
+          <t>463444</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>134109</t>
+          <t>137188</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>121877</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>148619</t>
+          <t>150497</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>100402</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>88256</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>233044</t>
+          <t>237590</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>215305</t>
+          <t>218992</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>254023</t>
+          <t>256090</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>59519</t>
+          <t>57104</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>73928</t>
+          <t>70373</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>63077</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50476</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77098</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>122403</t>
+          <t>120182</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>103473</t>
+          <t>102253</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>142292</t>
+          <t>137527</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -5039,17 +5039,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31446</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,27 +5335,27 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>452810</t>
+          <t>522928</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>426531</t>
+          <t>491654</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>480536</t>
+          <t>550133</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>769182</t>
+          <t>677877</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>735039</t>
+          <t>655192</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>813207</t>
+          <t>695503</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1221992</t>
+          <t>1200804</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1164053</t>
+          <t>1160707</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1315381</t>
+          <t>1231060</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>263493</t>
+          <t>315838</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>232972</t>
+          <t>284496</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>290632</t>
+          <t>344410</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>157019</t>
+          <t>182509</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>80451</t>
+          <t>163186</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>214781</t>
+          <t>204279</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>498346</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>273859</t>
+          <t>464147</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>501525</t>
+          <t>539259</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>182013</t>
+          <t>208562</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>154058</t>
+          <t>180544</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>211070</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>178513</t>
+          <t>209568</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>186008</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>246534</t>
+          <t>238492</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>360526</t>
+          <t>418130</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>231125</t>
+          <t>376033</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>437383</t>
+          <t>463396</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>31366</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>42014</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>48643</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41491</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>48346</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>69853</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>77566</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6173,32 +6173,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>22803</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>58900</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>295470</t>
+          <t>345719</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>132880</t>
+          <t>318914</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>414247</t>
+          <t>377711</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>667162</t>
+          <t>770160</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>651164</t>
+          <t>751254</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>679863</t>
+          <t>785598</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1115880</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>596991</t>
+          <t>1076302</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1143817</t>
+          <t>1154283</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>379752</t>
+          <t>439532</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>176532</t>
+          <t>410399</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>529436</t>
+          <t>470098</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>52769</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>66140</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>425575</t>
+          <t>492300</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>268264</t>
+          <t>456819</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>513137</t>
+          <t>531208</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>177305</t>
+          <t>210061</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>78528</t>
+          <t>179885</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>242259</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>154314</t>
+          <t>179534</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>135439</t>
+          <t>156692</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>177184</t>
+          <t>203843</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>331619</t>
+          <t>389595</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>211883</t>
+          <t>354096</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>399892</t>
+          <t>427576</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>36523</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>32141</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6968,32 +6968,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>250087</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>626993</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7003,67 +7003,67 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>18400</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>252264</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>776574</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -7198,32 +7198,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1192592</t>
+          <t>1665820</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1700703</t>
+          <t>1796052</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>614292</t>
+          <t>786819</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>843229</t>
+          <t>873757</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>2016671</t>
+          <t>2485627</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>2492035</t>
+          <t>2654563</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>712530</t>
+          <t>911085</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1001359</t>
+          <t>1044348</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>737230</t>
+          <t>897206</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1025692</t>
+          <t>1004927</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1611652</t>
+          <t>1834414</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>1974983</t>
+          <t>2009994</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>127027</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>167125</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>209298</t>
+          <t>241658</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>283026</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>85939</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>117979</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>99331</t>
+          <t>118070</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>143985</t>
+          <t>156332</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>186252</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>253087</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>42948</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>79977</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>130647</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7763,32 +7763,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>26808</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1057929</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7798,32 +7798,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7833,32 +7833,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>304014</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1050624</t>
+          <t>92180</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
